--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothroot.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothroot.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="111">
   <si>
     <t>Property</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>拡張値の値 - データ型の制約付きセットの1つでなければなりません（リストの[拡張性]（拡張性]（拡張性。html）を参照）。 / Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalRootBodyStructure_VS</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -688,7 +694,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.9765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1289,13 +1295,11 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1325,7 +1329,7 @@
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>103</v>

--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothroot.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-toothroot.xlsx
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:CodeableConcept</t>
+    <t>element:Observation.bodySite</t>
   </si>
   <si>
     <t>ID</t>
@@ -350,7 +350,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalRootBodyStructure_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalRootBodyStructure_VS</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -694,7 +694,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.9765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
